--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -518,6 +518,22 @@
     <t>Indicates whether emergency medical services prenotified the receiving hospital before arrival.</t>
   </si>
   <si>
+    <t>Encounter.extension:dischargeFacilityType</t>
+  </si>
+  <si>
+    <t>dischargeFacilityType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/discharge-facility-type-ext}
+</t>
+  </si>
+  <si>
+    <t>Type of facility or transfer destination after discharge</t>
+  </si>
+  <si>
+    <t>Type of facility or transfer destination receiving the patient at discharge.</t>
+  </si>
+  <si>
     <t>Encounter.extension:dischargeDepartmentService</t>
   </si>
   <si>
@@ -531,7 +547,7 @@
     <t>Discharge department, service or facility type</t>
   </si>
   <si>
-    <t>Department/service or facility type receiving the patient at discharge.</t>
+    <t>Department, unit or service receiving the patient at discharge.</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -1928,7 +1944,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN74"/>
+  <dimension ref="A1:AN75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.66015625" customWidth="true" bestFit="true"/>
@@ -3454,48 +3470,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="D14" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="O14" t="s" s="2">
-        <v>170</v>
-      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>81</v>
       </c>
@@ -3543,7 +3557,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3564,7 +3578,7 @@
         <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>81</v>
@@ -3572,14 +3586,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3592,22 +3606,26 @@
         <v>81</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>81</v>
       </c>
@@ -3655,7 +3673,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3667,27 +3685,27 @@
         <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>176</v>
+        <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
+      <c r="A16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AM15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3695,32 +3713,30 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -3730,7 +3746,7 @@
         <v>81</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>81</v>
@@ -3745,13 +3761,13 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -3769,13 +3785,13 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
@@ -3784,24 +3800,24 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3809,30 +3825,32 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3842,7 +3860,7 @@
         <v>81</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>81</v>
@@ -3857,13 +3875,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>195</v>
+        <v>114</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -3881,13 +3899,13 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
@@ -3896,24 +3914,24 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3924,25 +3942,25 @@
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3969,13 +3987,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -3993,13 +4011,13 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
@@ -4011,21 +4029,21 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4036,7 +4054,7 @@
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>81</v>
@@ -4045,20 +4063,18 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4083,13 +4099,13 @@
         <v>81</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>81</v>
@@ -4107,13 +4123,13 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>81</v>
@@ -4122,24 +4138,24 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4162,15 +4178,17 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4195,13 +4213,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4219,7 +4237,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4234,38 +4252,38 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>228</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>81</v>
@@ -4274,17 +4292,15 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4309,13 +4325,13 @@
         <v>81</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>81</v>
+        <v>229</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>81</v>
@@ -4333,13 +4349,13 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
@@ -4348,56 +4364,56 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>81</v>
+        <v>233</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4423,13 +4439,13 @@
         <v>81</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>81</v>
@@ -4447,7 +4463,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4462,24 +4478,24 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>81</v>
+        <v>238</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>81</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4490,7 +4506,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4499,18 +4515,20 @@
         <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4535,13 +4553,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -4559,13 +4577,13 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
@@ -4577,25 +4595,25 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>247</v>
+        <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>248</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4611,16 +4629,16 @@
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4671,7 +4689,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4686,28 +4704,28 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>254</v>
+        <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>81</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4726,13 +4744,13 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4783,7 +4801,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4798,13 +4816,13 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>81</v>
+        <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4812,10 +4830,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4826,7 +4844,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -4838,17 +4856,15 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N26" t="s" s="2">
         <v>264</v>
       </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -4897,13 +4913,13 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
@@ -4912,13 +4928,13 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>265</v>
+        <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
@@ -4926,10 +4942,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4952,15 +4968,17 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5009,7 +5027,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5024,24 +5042,24 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="AN27" t="s" s="2">
-        <v>273</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5052,7 +5070,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -5061,20 +5079,18 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>278</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5123,39 +5139,39 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>279</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5166,7 +5182,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -5175,18 +5191,20 @@
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5235,50 +5253,50 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5290,7 +5308,7 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>138</v>
+        <v>289</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>290</v>
@@ -5298,9 +5316,7 @@
       <c r="M30" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N30" t="s" s="2">
-        <v>169</v>
-      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5355,13 +5371,13 @@
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
@@ -5370,7 +5386,7 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5378,14 +5394,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>294</v>
+        <v>171</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5398,10 +5414,10 @@
         <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>138</v>
@@ -5413,11 +5429,9 @@
         <v>296</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5486,7 +5500,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5501,7 +5515,7 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5514,24 +5528,26 @@
         <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5555,31 +5571,31 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5588,30 +5604,30 @@
         <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>306</v>
+        <v>135</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5622,7 +5638,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -5631,18 +5647,20 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>309</v>
+        <v>197</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5667,13 +5685,13 @@
         <v>81</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>81</v>
+        <v>307</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>81</v>
+        <v>308</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>81</v>
@@ -5691,39 +5709,39 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5743,20 +5761,18 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>318</v>
-      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5805,7 +5821,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5814,30 +5830,30 @@
         <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>271</v>
+        <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>319</v>
+        <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5848,7 +5864,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -5860,15 +5876,17 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -5917,39 +5935,39 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>81</v>
+        <v>324</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>327</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5969,20 +5987,18 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>332</v>
-      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6031,7 +6047,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6046,16 +6062,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>81</v>
+        <v>259</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>135</v>
+        <v>331</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>81</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -6074,7 +6090,7 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -6086,16 +6102,16 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6151,7 +6167,7 @@
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
@@ -6160,24 +6176,24 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>338</v>
+        <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>339</v>
+        <v>135</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>340</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6200,15 +6216,17 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>342</v>
+        <v>314</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6257,7 +6275,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6272,13 +6290,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>81</v>
+        <v>344</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>345</v>
@@ -6312,13 +6330,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6393,15 +6411,15 @@
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6424,7 +6442,7 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>352</v>
@@ -6432,9 +6450,7 @@
       <c r="M40" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="N40" t="s" s="2">
-        <v>354</v>
-      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6483,7 +6499,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6498,24 +6514,24 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>355</v>
+        <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6526,7 +6542,7 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6535,19 +6551,19 @@
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>275</v>
+        <v>356</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6597,13 +6613,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6612,24 +6628,24 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>81</v>
+        <v>360</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>81</v>
+        <v>361</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6640,7 +6656,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -6649,18 +6665,20 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>285</v>
+        <v>363</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6709,19 +6727,19 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>287</v>
+        <v>362</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
@@ -6730,7 +6748,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -6738,21 +6756,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -6764,7 +6782,7 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>138</v>
+        <v>289</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>290</v>
@@ -6772,9 +6790,7 @@
       <c r="M43" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N43" t="s" s="2">
-        <v>169</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6829,13 +6845,13 @@
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
@@ -6844,7 +6860,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -6852,14 +6868,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>294</v>
+        <v>171</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6872,10 +6888,10 @@
         <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>138</v>
@@ -6887,11 +6903,9 @@
         <v>296</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -6960,7 +6974,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -6968,14 +6982,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6988,22 +7002,26 @@
         <v>81</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>365</v>
+        <v>300</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7027,11 +7045,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>367</v>
+        <v>81</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -7049,7 +7069,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>302</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7061,7 +7081,7 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
@@ -7070,7 +7090,7 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7078,14 +7098,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>369</v>
+        <v>81</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7104,13 +7124,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7137,13 +7157,11 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7161,7 +7179,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7176,28 +7194,28 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>375</v>
+        <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>378</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7216,17 +7234,15 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>275</v>
+        <v>375</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7251,13 +7267,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>81</v>
+        <v>378</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7275,7 +7291,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7290,16 +7306,16 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -7318,7 +7334,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7327,18 +7343,20 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7387,19 +7405,19 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>287</v>
+        <v>384</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7408,7 +7426,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>225</v>
+        <v>388</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7416,21 +7434,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7442,7 +7460,7 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>138</v>
+        <v>289</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>290</v>
@@ -7450,9 +7468,7 @@
       <c r="M49" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>169</v>
-      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -7507,13 +7523,13 @@
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -7522,7 +7538,7 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7530,14 +7546,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>294</v>
+        <v>171</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7550,10 +7566,10 @@
         <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>138</v>
@@ -7565,11 +7581,9 @@
         <v>296</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7638,7 +7652,7 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -7646,14 +7660,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>388</v>
+        <v>299</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7666,22 +7680,26 @@
         <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>389</v>
+        <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7705,11 +7723,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -7727,7 +7747,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>387</v>
+        <v>302</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7739,31 +7759,31 @@
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>375</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>376</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>393</v>
+        <v>135</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>394</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7779,16 +7799,16 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>192</v>
+        <v>394</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7815,13 +7835,11 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -7839,7 +7857,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7854,24 +7872,24 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>225</v>
+        <v>398</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7894,17 +7912,15 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -7929,13 +7945,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -7953,7 +7969,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7974,18 +7990,18 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>406</v>
+        <v>230</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>81</v>
+        <v>405</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8008,7 +8024,7 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>192</v>
+        <v>407</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>408</v>
@@ -8019,9 +8035,7 @@
       <c r="N54" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="O54" t="s" s="2">
-        <v>411</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8045,13 +8059,13 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>412</v>
+        <v>81</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8069,7 +8083,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8090,18 +8104,18 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8124,16 +8138,20 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8157,13 +8175,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8181,7 +8199,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8202,18 +8220,18 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8236,17 +8254,15 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8271,13 +8287,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8295,7 +8311,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8316,18 +8332,18 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8338,10 +8354,10 @@
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>81</v>
@@ -8350,16 +8366,16 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>275</v>
+        <v>197</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8385,13 +8401,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>81</v>
+        <v>433</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8409,13 +8425,13 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
@@ -8430,13 +8446,13 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AN57" t="s" s="2">
-        <v>81</v>
-      </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>436</v>
       </c>
@@ -8455,7 +8471,7 @@
         <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>81</v>
@@ -8464,15 +8480,17 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>285</v>
+        <v>437</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8521,7 +8539,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>287</v>
+        <v>436</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8530,10 +8548,10 @@
         <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
@@ -8542,7 +8560,7 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>225</v>
+        <v>440</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -8550,21 +8568,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
@@ -8576,7 +8594,7 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>138</v>
+        <v>289</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>290</v>
@@ -8584,9 +8602,7 @@
       <c r="M59" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N59" t="s" s="2">
-        <v>169</v>
-      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -8641,13 +8657,13 @@
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -8656,7 +8672,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -8664,14 +8680,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>294</v>
+        <v>171</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8684,10 +8700,10 @@
         <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>138</v>
@@ -8699,11 +8715,9 @@
         <v>296</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -8772,7 +8786,7 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -8780,42 +8794,46 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>440</v>
+        <v>300</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
       </c>
@@ -8863,19 +8881,19 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>439</v>
+        <v>302</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
@@ -8884,18 +8902,18 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>178</v>
+        <v>135</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8918,7 +8936,7 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>444</v>
+        <v>178</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>445</v>
@@ -8975,7 +8993,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8996,13 +9014,13 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AN62" t="s" s="2">
-        <v>81</v>
-      </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>448</v>
       </c>
@@ -9021,7 +9039,7 @@
         <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>81</v>
@@ -9030,13 +9048,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>192</v>
+        <v>449</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9063,11 +9081,13 @@
         <v>81</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -9109,15 +9129,15 @@
         <v>452</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
         <v>453</v>
       </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9131,7 +9151,7 @@
         <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>81</v>
@@ -9140,13 +9160,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9173,13 +9193,11 @@
         <v>81</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
@@ -9197,7 +9215,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9218,18 +9236,18 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>225</v>
+        <v>457</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9252,13 +9270,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>444</v>
+        <v>197</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9285,13 +9303,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>81</v>
+        <v>462</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9309,7 +9327,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9330,13 +9348,13 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>463</v>
+        <v>230</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>464</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>465</v>
       </c>
@@ -9355,7 +9373,7 @@
         <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>81</v>
@@ -9364,7 +9382,7 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>192</v>
+        <v>449</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>466</v>
@@ -9397,11 +9415,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9440,18 +9460,18 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>470</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9462,7 +9482,7 @@
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>91</v>
@@ -9474,17 +9494,15 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>275</v>
+        <v>197</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>474</v>
-      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -9509,13 +9527,11 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -9533,13 +9549,13 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
@@ -9554,13 +9570,13 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AN67" t="s" s="2">
-        <v>81</v>
-      </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>476</v>
       </c>
@@ -9576,10 +9592,10 @@
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>81</v>
@@ -9588,15 +9604,17 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>285</v>
+        <v>477</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -9645,19 +9663,19 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>287</v>
+        <v>476</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
@@ -9666,7 +9684,7 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>225</v>
+        <v>480</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -9674,21 +9692,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -9700,7 +9718,7 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>138</v>
+        <v>289</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>290</v>
@@ -9708,9 +9726,7 @@
       <c r="M69" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N69" t="s" s="2">
-        <v>169</v>
-      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9765,13 +9781,13 @@
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>81</v>
@@ -9780,7 +9796,7 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -9788,14 +9804,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>294</v>
+        <v>171</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9808,10 +9824,10 @@
         <v>81</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>138</v>
@@ -9823,11 +9839,9 @@
         <v>296</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
@@ -9896,7 +9910,7 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -9904,42 +9918,46 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>480</v>
+        <v>138</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>481</v>
+        <v>300</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
       </c>
@@ -9987,39 +10005,39 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>479</v>
+        <v>302</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>484</v>
+        <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>320</v>
+        <v>135</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>485</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10027,7 +10045,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>90</v>
@@ -10042,17 +10060,15 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>110</v>
+        <v>485</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M72" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10077,13 +10093,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>490</v>
+        <v>81</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>491</v>
+        <v>81</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -10101,10 +10117,10 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>90</v>
@@ -10116,24 +10132,24 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>492</v>
+        <v>325</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>81</v>
+        <v>490</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10156,16 +10172,16 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10191,13 +10207,13 @@
         <v>81</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>204</v>
+        <v>114</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>81</v>
@@ -10215,7 +10231,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10236,7 +10252,7 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -10244,10 +10260,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10270,15 +10286,17 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>309</v>
+        <v>197</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -10303,13 +10321,13 @@
         <v>81</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
@@ -10327,7 +10345,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10348,14 +10366,126 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>312</v>
+        <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN74">
+  <autoFilter ref="A1:AN75">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10365,7 +10495,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI73">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/stroke-encounter-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -476,7 +476,7 @@
     <t>firstHospital</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/first-hospital-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/first-hospital-ext}
 </t>
   </si>
   <si>
@@ -492,7 +492,7 @@
     <t>requiredPostAcuteCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/required-post-acute-care-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/required-post-acute-care-ext}
 </t>
   </si>
   <si>
@@ -508,7 +508,7 @@
     <t>emsPrenotification</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/ems-prenotification-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/ems-prenotification-ext}
 </t>
   </si>
   <si>
@@ -524,7 +524,7 @@
     <t>dischargeFacilityType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/discharge-facility-type-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/discharge-facility-type-ext}
 </t>
   </si>
   <si>
@@ -540,7 +540,7 @@
     <t>dischargeDepartmentService</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/discharge-department-service-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/discharge-department-service-ext}
 </t>
   </si>
   <si>
@@ -748,7 +748,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -1471,7 +1471,7 @@
     <t>From where patient was admitted (physician referral, transfer).</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/admission-pathway-vs</t>
+    <t>http://qualityregistry.org/ValueSet/admission-pathway-vs</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -1522,7 +1522,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/discharge-destination-vs</t>
+    <t>http://qualityregistry.org/ValueSet/discharge-destination-vs</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-encounter-profile.xlsx
+++ b/StructureDefinition-stroke-encounter-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
